--- a/data/trans_orig/P25A$medico-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P25A$medico-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según motivo para dejar de fumar (multirrespuesta) en 2007</t>
+          <t>Población según motivo para dejar de fumar (multirrespuesta) en 2007 (tasa de respuesta: 98,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>96862</t>
+          <t>97029</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>130251</t>
+          <t>128440</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2937</t>
+          <t>2978</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12734</t>
+          <t>12748</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>102204</t>
+          <t>103824</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>138627</t>
+          <t>136105</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>38,75%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43419</t>
+          <t>42932</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69929</t>
+          <t>69770</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>1978</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11017</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48573</t>
+          <t>48818</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>76553</t>
+          <t>78016</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,21%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10858</t>
+          <t>11428</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27007</t>
+          <t>27148</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>4686</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11774</t>
+          <t>12095</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29324</t>
+          <t>29239</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6336</t>
+          <t>5937</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19658</t>
+          <t>18474</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>7140</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7609</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21509</t>
+          <t>20610</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>128881</t>
+          <t>129897</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>163256</t>
+          <t>163402</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>29763</t>
+          <t>30126</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41659</t>
+          <t>41483</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>163495</t>
+          <t>164834</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>201020</t>
+          <t>200512</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,09%</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2930</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14466</t>
+          <t>14972</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1312,12 +1312,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3369</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3790</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>16049</t>
+          <t>16519</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35106</t>
+          <t>33556</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59108</t>
+          <t>57591</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>6090</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19932</t>
+          <t>19168</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42972</t>
+          <t>42391</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72022</t>
+          <t>71433</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37562</t>
+          <t>37959</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63942</t>
+          <t>62318</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15145</t>
+          <t>15523</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31693</t>
+          <t>33759</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>58112</t>
+          <t>57541</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>89406</t>
+          <t>88567</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,81%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13077</t>
+          <t>12924</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31567</t>
+          <t>31291</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9152</t>
+          <t>9410</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24788</t>
+          <t>25089</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>26312</t>
+          <t>26395</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>49242</t>
+          <t>50176</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2807</t>
+          <t>2837</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13137</t>
+          <t>13378</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2862</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13046</t>
+          <t>13626</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7446</t>
+          <t>7263</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21604</t>
+          <t>21255</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>137176</t>
+          <t>139548</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>167935</t>
+          <t>170448</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>82999</t>
+          <t>84590</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>107446</t>
+          <t>107969</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>232295</t>
+          <t>230407</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>270328</t>
+          <t>269804</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,49%</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10159</t>
+          <t>9460</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15056</t>
+          <t>15400</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33244</t>
+          <t>34251</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>18609</t>
+          <t>18779</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>39329</t>
+          <t>38836</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5115</t>
+          <t>5606</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18537</t>
+          <t>19006</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>960</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7873</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7703</t>
+          <t>7219</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23194</t>
+          <t>22203</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6168</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19538</t>
+          <t>19643</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4071</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14228</t>
+          <t>14512</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11692</t>
+          <t>12906</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29361</t>
+          <t>28947</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4551</t>
+          <t>4653</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15279</t>
+          <t>15834</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9587</t>
+          <t>8881</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6827</t>
+          <t>6775</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>21026</t>
+          <t>20349</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>14,98%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6417</t>
+          <t>6214</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>932</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>9054</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2744</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11345</t>
+          <t>12570</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49248</t>
+          <t>48955</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66513</t>
+          <t>66254</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26808</t>
+          <t>25618</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39464</t>
+          <t>39577</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>79250</t>
+          <t>80680</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>102148</t>
+          <t>102110</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,19%</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>823</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>7791</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9801</t>
+          <t>9354</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2548</t>
+          <t>2782</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>13226</t>
+          <t>14124</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>146547</t>
+          <t>148595</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>191499</t>
+          <t>191333</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13395</t>
+          <t>12894</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33379</t>
+          <t>30914</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>166235</t>
+          <t>166517</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>214789</t>
+          <t>214680</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>98278</t>
+          <t>99837</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>136992</t>
+          <t>137503</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>26066</t>
+          <t>25904</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>48311</t>
+          <t>47492</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>133501</t>
+          <t>132571</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>178395</t>
+          <t>176070</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,12%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36167</t>
+          <t>35340</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>62083</t>
+          <t>63240</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13204</t>
+          <t>12250</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>31723</t>
+          <t>30475</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>53133</t>
+          <t>52820</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>86402</t>
+          <t>86850</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13128</t>
+          <t>12841</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>30466</t>
+          <t>29474</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7348</t>
+          <t>6940</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21121</t>
+          <t>21806</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>23317</t>
+          <t>23224</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>43831</t>
+          <t>43983</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>334485</t>
+          <t>334505</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>382759</t>
+          <t>382484</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>150391</t>
+          <t>150536</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>181985</t>
+          <t>181390</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>494708</t>
+          <t>495184</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>553869</t>
+          <t>552332</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>63,1%</t>
         </is>
       </c>
     </row>
@@ -3343,12 +3343,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8406</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>24022</t>
+          <t>24256</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3358,12 +3358,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>18170</t>
+          <t>18981</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>38337</t>
+          <t>39836</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>30420</t>
+          <t>30197</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>56623</t>
+          <t>55524</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según motivo para dejar de fumar (multirrespuesta) en 2012</t>
+          <t>Población según motivo para dejar de fumar (multirrespuesta) en 2012 (tasa de respuesta: 97,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89777</t>
+          <t>89625</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>127273</t>
+          <t>125805</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7999</t>
+          <t>8458</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21488</t>
+          <t>22087</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>102491</t>
+          <t>103536</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>142544</t>
+          <t>142520</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32255</t>
+          <t>33701</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58466</t>
+          <t>60284</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>6950</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34659</t>
+          <t>34427</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>61718</t>
+          <t>61203</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14573</t>
+          <t>14529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34108</t>
+          <t>35227</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>943</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8082</t>
+          <t>8184</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16589</t>
+          <t>16718</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>37251</t>
+          <t>37921</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4087</t>
+          <t>4406</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17833</t>
+          <t>18612</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6786</t>
+          <t>7096</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6268</t>
+          <t>6050</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21426</t>
+          <t>21059</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>197834</t>
+          <t>197535</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>236991</t>
+          <t>238601</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>41731</t>
+          <t>40555</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>56523</t>
+          <t>55864</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>246343</t>
+          <t>246636</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>290856</t>
+          <t>288472</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>65,39%</t>
         </is>
       </c>
     </row>
@@ -4256,12 +4256,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2957</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16491</t>
+          <t>15463</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4271,12 +4271,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4291,12 +4291,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>997</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8308</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5113</t>
+          <t>5018</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>20792</t>
+          <t>19160</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30491</t>
+          <t>31712</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57055</t>
+          <t>56894</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10465</t>
+          <t>10762</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29566</t>
+          <t>28852</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46723</t>
+          <t>46291</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78488</t>
+          <t>77219</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26063</t>
+          <t>25312</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49604</t>
+          <t>49763</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12530</t>
+          <t>12660</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31489</t>
+          <t>31292</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41383</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>72309</t>
+          <t>72172</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21169</t>
+          <t>20361</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42574</t>
+          <t>43778</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11377</t>
+          <t>11395</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30598</t>
+          <t>30372</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>37744</t>
+          <t>36933</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>66656</t>
+          <t>66521</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11253</t>
+          <t>10608</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28087</t>
+          <t>27169</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1776</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13725</t>
+          <t>14812</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14348</t>
+          <t>14789</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34213</t>
+          <t>34948</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>238831</t>
+          <t>238108</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>272175</t>
+          <t>272526</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>173781</t>
+          <t>173987</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>200222</t>
+          <t>201697</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>420405</t>
+          <t>425068</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>465135</t>
+          <t>465624</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,21%</t>
         </is>
       </c>
     </row>
@@ -4938,12 +4938,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14923</t>
+          <t>15297</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4953,12 +4953,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4973,12 +4973,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7834</t>
+          <t>7923</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23346</t>
+          <t>23371</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4988,12 +4988,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5008,12 +5008,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>13425</t>
+          <t>14216</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>32720</t>
+          <t>32786</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5023,12 +5023,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19299</t>
+          <t>19589</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>6814</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>6326</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22272</t>
+          <t>22481</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>2302</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12166</t>
+          <t>12775</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20375</t>
+          <t>19486</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11081</t>
+          <t>10683</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27728</t>
+          <t>28325</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4135</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16165</t>
+          <t>16778</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>4137</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15208</t>
+          <t>15864</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11474</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>27482</t>
+          <t>27953</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>854</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8342</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10782</t>
+          <t>10505</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13873</t>
+          <t>15346</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>63724</t>
+          <t>63881</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>82423</t>
+          <t>81351</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>53469</t>
+          <t>53714</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>67745</t>
+          <t>68090</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>122697</t>
+          <t>123390</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>145471</t>
+          <t>145637</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,86%</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6696</t>
+          <t>6494</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6289</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>972</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9867</t>
+          <t>9842</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>137926</t>
+          <t>138297</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>184183</t>
+          <t>185369</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24372</t>
+          <t>24164</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47132</t>
+          <t>47385</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>167872</t>
+          <t>169939</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>222191</t>
+          <t>222787</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>69519</t>
+          <t>69852</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>107720</t>
+          <t>104258</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24537</t>
+          <t>23883</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>49587</t>
+          <t>48479</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>100155</t>
+          <t>100440</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>143504</t>
+          <t>145462</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>48967</t>
+          <t>48425</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>81135</t>
+          <t>80815</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21379</t>
+          <t>20743</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>43687</t>
+          <t>43260</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>76504</t>
+          <t>76378</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>117461</t>
+          <t>117202</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19923</t>
+          <t>20728</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42768</t>
+          <t>43390</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6864</t>
+          <t>6521</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21879</t>
+          <t>20973</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30754</t>
+          <t>30736</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>58175</t>
+          <t>57019</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>523706</t>
+          <t>520980</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>578177</t>
+          <t>577329</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>281802</t>
+          <t>282067</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>316349</t>
+          <t>314939</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>816026</t>
+          <t>815047</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>881413</t>
+          <t>880525</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,22%</t>
         </is>
       </c>
     </row>
@@ -6302,12 +6302,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>10634</t>
+          <t>9690</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>29115</t>
+          <t>27799</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6317,12 +6317,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6337,12 +6337,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>11097</t>
+          <t>12242</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>28684</t>
+          <t>29632</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6352,12 +6352,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6372,12 +6372,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>25667</t>
+          <t>25339</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>51431</t>
+          <t>49613</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6387,12 +6387,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según motivo para dejar de fumar (multirrespuesta) en 2016</t>
+          <t>Población según motivo para dejar de fumar (multirrespuesta) en 2016 (tasa de respuesta: 79,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41811</t>
+          <t>42243</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>65548</t>
+          <t>66307</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>933</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>7271</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44525</t>
+          <t>44000</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69195</t>
+          <t>69486</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,08%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29979</t>
+          <t>30595</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51643</t>
+          <t>52262</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3733</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14368</t>
+          <t>14033</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37324</t>
+          <t>37731</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>61522</t>
+          <t>62753</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,36%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10430</t>
+          <t>10760</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27115</t>
+          <t>26604</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10160</t>
+          <t>10222</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14392</t>
+          <t>14651</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>33090</t>
+          <t>32428</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,11%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5861</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18914</t>
+          <t>18080</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4369</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6750</t>
+          <t>6684</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20034</t>
+          <t>20319</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>93750</t>
+          <t>94190</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>122135</t>
+          <t>122147</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17505</t>
+          <t>17488</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29289</t>
+          <t>29413</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>116171</t>
+          <t>115761</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>146789</t>
+          <t>145367</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>58,75%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13477</t>
+          <t>13708</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31500</t>
+          <t>31167</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1707</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11734</t>
+          <t>10772</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>16814</t>
+          <t>16956</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>36873</t>
+          <t>37073</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,98%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37233</t>
+          <t>37724</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64106</t>
+          <t>65749</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13529</t>
+          <t>14678</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32115</t>
+          <t>32842</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57604</t>
+          <t>57237</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91110</t>
+          <t>89695</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35594</t>
+          <t>35531</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60748</t>
+          <t>61192</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18617</t>
+          <t>19157</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39369</t>
+          <t>39030</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56984</t>
+          <t>59979</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>91840</t>
+          <t>90670</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28440</t>
+          <t>26764</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52390</t>
+          <t>52113</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6604</t>
+          <t>6728</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20410</t>
+          <t>21025</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>37518</t>
+          <t>36874</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>65745</t>
+          <t>65585</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7529</t>
+          <t>7043</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22693</t>
+          <t>22281</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,44 +7686,44 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,38%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>9871</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5007</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>17409</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>4,91%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>2,49%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,51%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>9871</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>5111</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>17418</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,91%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
           <t>8,66%</t>
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15136</t>
+          <t>14912</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34161</t>
+          <t>33960</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>174170</t>
+          <t>174536</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>209360</t>
+          <t>206797</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>121392</t>
+          <t>121881</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>147799</t>
+          <t>148855</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>304150</t>
+          <t>303038</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>348676</t>
+          <t>346791</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>68,93%</t>
         </is>
       </c>
     </row>
@@ -7897,12 +7897,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17778</t>
+          <t>18177</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36979</t>
+          <t>38528</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7912,12 +7912,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7932,12 +7932,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17234</t>
+          <t>17314</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>36611</t>
+          <t>36640</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7947,12 +7947,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7967,12 +7967,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>40233</t>
+          <t>39548</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>67408</t>
+          <t>67430</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>5816</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20330</t>
+          <t>21152</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10999</t>
+          <t>10580</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9930</t>
+          <t>10348</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26274</t>
+          <t>27274</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>2366</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15658</t>
+          <t>14782</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16716</t>
+          <t>16951</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9911</t>
+          <t>10743</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26777</t>
+          <t>28419</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>15,39%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8944</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25325</t>
+          <t>24667</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5056</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16930</t>
+          <t>17371</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17050</t>
+          <t>16697</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>37201</t>
+          <t>39307</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12964</t>
+          <t>12475</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,47 +8368,47 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>13,92%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>5200</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>11442</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>5,47%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
           <t>2,16%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>14,47%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>5200</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>11677</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>5,47%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5580</t>
+          <t>5666</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19754</t>
+          <t>18368</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51803</t>
+          <t>50966</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>70790</t>
+          <t>70977</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>64946</t>
+          <t>64814</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>80735</t>
+          <t>80691</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>122897</t>
+          <t>121674</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>148888</t>
+          <t>148071</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,18%</t>
         </is>
       </c>
     </row>
@@ -8579,12 +8579,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4086</t>
+          <t>4907</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16037</t>
+          <t>16715</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8594,12 +8594,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8614,12 +8614,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6847</t>
+          <t>7307</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21162</t>
+          <t>22252</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8649,12 +8649,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14768</t>
+          <t>13820</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>33832</t>
+          <t>33253</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>96472</t>
+          <t>97948</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>136205</t>
+          <t>137652</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20931</t>
+          <t>21228</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42491</t>
+          <t>43145</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>122138</t>
+          <t>124792</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>168766</t>
+          <t>168185</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,98%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>76294</t>
+          <t>78131</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>112714</t>
+          <t>114668</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>33513</t>
+          <t>34005</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>59302</t>
+          <t>60149</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>118159</t>
+          <t>118433</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>162689</t>
+          <t>163259</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,46%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>55487</t>
+          <t>55773</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>89362</t>
+          <t>90145</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19049</t>
+          <t>18750</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>39737</t>
+          <t>39519</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>81931</t>
+          <t>81016</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>119536</t>
+          <t>118496</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20385</t>
+          <t>20920</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>43442</t>
+          <t>43763</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9840</t>
+          <t>9269</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25657</t>
+          <t>25349</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>35388</t>
+          <t>34781</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>60879</t>
+          <t>60749</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>335912</t>
+          <t>336690</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>384293</t>
+          <t>384581</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>213512</t>
+          <t>213924</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>247041</t>
+          <t>247900</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>563957</t>
+          <t>564407</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>621868</t>
+          <t>625936</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,93%</t>
         </is>
       </c>
     </row>
@@ -9261,12 +9261,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>45105</t>
+          <t>44180</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>74005</t>
+          <t>71387</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9296,12 +9296,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>33337</t>
+          <t>31290</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>57623</t>
+          <t>57955</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9331,12 +9331,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>82011</t>
+          <t>82783</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>119549</t>
+          <t>120963</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,93%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25A$medico-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P25A$medico-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>97029</t>
+          <t>96164</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>128440</t>
+          <t>129536</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2978</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12748</t>
+          <t>13214</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>103824</t>
+          <t>103925</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>136105</t>
+          <t>138708</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>39,49%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42932</t>
+          <t>44161</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69770</t>
+          <t>70061</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>2736</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11006</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48818</t>
+          <t>49636</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>78016</t>
+          <t>76311</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>21,73%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11428</t>
+          <t>11635</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27148</t>
+          <t>27665</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4686</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12095</t>
+          <t>11841</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29239</t>
+          <t>29251</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5937</t>
+          <t>6262</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18474</t>
+          <t>18749</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7140</t>
+          <t>6331</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7292</t>
+          <t>7384</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20610</t>
+          <t>20384</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>129897</t>
+          <t>130894</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>163402</t>
+          <t>164376</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30126</t>
+          <t>30402</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41483</t>
+          <t>41379</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>164834</t>
+          <t>164605</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>200512</t>
+          <t>201412</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,35%</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>3219</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14972</t>
+          <t>14660</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1312,12 +1312,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>3370</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>16519</t>
+          <t>16157</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33556</t>
+          <t>35716</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57591</t>
+          <t>59150</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6090</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19168</t>
+          <t>19606</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42391</t>
+          <t>45038</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71433</t>
+          <t>71736</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,48%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37959</t>
+          <t>38328</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62318</t>
+          <t>62703</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15523</t>
+          <t>14389</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33759</t>
+          <t>32915</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>57541</t>
+          <t>58513</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>88567</t>
+          <t>90232</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12924</t>
+          <t>13613</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31291</t>
+          <t>31202</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9410</t>
+          <t>9178</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25089</t>
+          <t>24971</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>26395</t>
+          <t>26816</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>50176</t>
+          <t>51297</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2837</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13378</t>
+          <t>13249</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2810</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13626</t>
+          <t>13049</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7263</t>
+          <t>7669</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21255</t>
+          <t>22154</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>139548</t>
+          <t>139227</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>170448</t>
+          <t>168061</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>84590</t>
+          <t>82712</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>107969</t>
+          <t>108060</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>230407</t>
+          <t>231233</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>269804</t>
+          <t>267131</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>68,8%</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9460</t>
+          <t>10821</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15400</t>
+          <t>15447</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>34251</t>
+          <t>33685</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2029,47 +2029,47 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
+          <t>10,22%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>22,28%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>27262</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>19002</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>39510</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>7,02%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
           <t>10,18%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>22,65%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>27262</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>18779</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>38836</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>7,02%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>4,84%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
-        <is>
-          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>5119</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19006</t>
+          <t>18754</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>967</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>7222</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7219</t>
+          <t>7147</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22203</t>
+          <t>21312</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6015</t>
+          <t>5852</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19643</t>
+          <t>19650</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14512</t>
+          <t>14244</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12906</t>
+          <t>13008</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28947</t>
+          <t>29129</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4653</t>
+          <t>3790</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15834</t>
+          <t>15038</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8881</t>
+          <t>9674</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6775</t>
+          <t>6658</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20349</t>
+          <t>21123</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,55%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6214</t>
+          <t>6498</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>948</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9054</t>
+          <t>9461</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>2081</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12570</t>
+          <t>11625</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48955</t>
+          <t>48719</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66254</t>
+          <t>66627</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25618</t>
+          <t>26247</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39577</t>
+          <t>40109</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>80680</t>
+          <t>80026</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>102110</t>
+          <t>102425</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,43%</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>826</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7791</t>
+          <t>7132</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>968</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9354</t>
+          <t>8263</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>14124</t>
+          <t>13954</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>148595</t>
+          <t>148718</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>191333</t>
+          <t>190845</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12894</t>
+          <t>13457</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30914</t>
+          <t>31506</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>166517</t>
+          <t>166531</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>214680</t>
+          <t>214916</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>99837</t>
+          <t>99299</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>137503</t>
+          <t>139156</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>25904</t>
+          <t>26767</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47492</t>
+          <t>48486</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>132571</t>
+          <t>133355</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>176070</t>
+          <t>177937</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,33%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35340</t>
+          <t>36141</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>63240</t>
+          <t>63195</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12250</t>
+          <t>13218</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30475</t>
+          <t>31847</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>52820</t>
+          <t>53517</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>86850</t>
+          <t>85331</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12841</t>
+          <t>13057</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29474</t>
+          <t>30053</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6940</t>
+          <t>7051</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21806</t>
+          <t>20533</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>23224</t>
+          <t>22869</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>43983</t>
+          <t>44669</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>334505</t>
+          <t>336313</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>382484</t>
+          <t>385026</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>150536</t>
+          <t>150598</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>181390</t>
+          <t>180176</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>495184</t>
+          <t>494299</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>552332</t>
+          <t>553554</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,24%</t>
         </is>
       </c>
     </row>
@@ -3343,12 +3343,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>24256</t>
+          <t>23471</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3358,12 +3358,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>18981</t>
+          <t>18728</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>39836</t>
+          <t>38528</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>30197</t>
+          <t>30810</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>55524</t>
+          <t>55759</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89625</t>
+          <t>89579</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>125805</t>
+          <t>125280</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8458</t>
+          <t>8318</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22087</t>
+          <t>21674</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>103536</t>
+          <t>102458</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>142520</t>
+          <t>140444</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>31,84%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33701</t>
+          <t>32422</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60284</t>
+          <t>58041</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6950</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34427</t>
+          <t>34900</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>61203</t>
+          <t>60974</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14529</t>
+          <t>13462</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35227</t>
+          <t>33191</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>901</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8184</t>
+          <t>7812</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16718</t>
+          <t>16561</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>37921</t>
+          <t>37777</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4406</t>
+          <t>4071</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18612</t>
+          <t>18200</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7096</t>
+          <t>6688</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6050</t>
+          <t>5726</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21059</t>
+          <t>20614</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>197535</t>
+          <t>199902</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>238601</t>
+          <t>235451</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40555</t>
+          <t>41664</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55864</t>
+          <t>56699</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>246636</t>
+          <t>247253</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>288472</t>
+          <t>289650</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,66%</t>
         </is>
       </c>
     </row>
@@ -4256,12 +4256,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15463</t>
+          <t>15551</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4271,12 +4271,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4291,12 +4291,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>995</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5018</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19160</t>
+          <t>20818</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31712</t>
+          <t>31796</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56894</t>
+          <t>57416</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10762</t>
+          <t>10362</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28852</t>
+          <t>28759</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46291</t>
+          <t>47375</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77219</t>
+          <t>77132</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25312</t>
+          <t>25122</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49763</t>
+          <t>48462</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12660</t>
+          <t>12043</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31292</t>
+          <t>32185</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41099</t>
+          <t>41307</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>72172</t>
+          <t>72378</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,31%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20361</t>
+          <t>21789</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43778</t>
+          <t>45729</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11395</t>
+          <t>11393</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30372</t>
+          <t>29400</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>36933</t>
+          <t>36701</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>66521</t>
+          <t>65981</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,22%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10608</t>
+          <t>10997</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27169</t>
+          <t>26988</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14812</t>
+          <t>13061</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14789</t>
+          <t>15074</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34948</t>
+          <t>34674</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>238108</t>
+          <t>240090</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>272526</t>
+          <t>273023</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>173987</t>
+          <t>173931</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>201697</t>
+          <t>201372</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>425068</t>
+          <t>421310</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>465624</t>
+          <t>464930</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,09%</t>
         </is>
       </c>
     </row>
@@ -4938,12 +4938,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3899</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15297</t>
+          <t>14472</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4953,12 +4953,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4973,12 +4973,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7923</t>
+          <t>7210</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23371</t>
+          <t>22334</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4988,12 +4988,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5008,12 +5008,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>14216</t>
+          <t>14593</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>32786</t>
+          <t>32407</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5023,12 +5023,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>5884</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19589</t>
+          <t>19610</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6814</t>
+          <t>7255</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6326</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22481</t>
+          <t>23990</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,81%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2302</t>
+          <t>2283</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12775</t>
+          <t>12896</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>6207</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19486</t>
+          <t>19978</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10683</t>
+          <t>11401</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28325</t>
+          <t>27113</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>15,61%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4292</t>
+          <t>4368</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16778</t>
+          <t>15795</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>4650</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15864</t>
+          <t>15857</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11096</t>
+          <t>11068</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>27953</t>
+          <t>27561</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,87%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>886</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7868</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10505</t>
+          <t>11051</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3056</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15346</t>
+          <t>14278</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>63881</t>
+          <t>64006</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>81351</t>
+          <t>81632</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>53714</t>
+          <t>54142</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>68090</t>
+          <t>67586</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>123390</t>
+          <t>122507</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>145637</t>
+          <t>145215</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,62%</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6494</t>
+          <t>6564</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>7379</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>976</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9842</t>
+          <t>9360</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>138297</t>
+          <t>138274</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>185369</t>
+          <t>185072</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24164</t>
+          <t>23978</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47385</t>
+          <t>46866</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>169939</t>
+          <t>169436</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>222787</t>
+          <t>221388</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,41%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>69852</t>
+          <t>70060</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>104258</t>
+          <t>105400</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>23883</t>
+          <t>23031</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>48479</t>
+          <t>48870</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>100440</t>
+          <t>99887</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>145462</t>
+          <t>144016</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>48425</t>
+          <t>48021</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>80815</t>
+          <t>80630</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>20743</t>
+          <t>21302</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>43260</t>
+          <t>45371</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>76378</t>
+          <t>76889</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>117202</t>
+          <t>116045</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20728</t>
+          <t>21455</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>43390</t>
+          <t>43465</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6521</t>
+          <t>7246</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20973</t>
+          <t>23098</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30736</t>
+          <t>31715</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>57019</t>
+          <t>59310</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>520980</t>
+          <t>521546</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>577329</t>
+          <t>576324</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>282067</t>
+          <t>283419</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>314939</t>
+          <t>315071</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>815047</t>
+          <t>817611</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>880525</t>
+          <t>883544</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,47%</t>
         </is>
       </c>
     </row>
@@ -6302,12 +6302,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>9690</t>
+          <t>8965</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>27799</t>
+          <t>27330</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6317,12 +6317,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6337,12 +6337,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>12242</t>
+          <t>11235</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>29632</t>
+          <t>29119</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6352,12 +6352,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6372,12 +6372,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>25339</t>
+          <t>24869</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>49613</t>
+          <t>48291</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6387,12 +6387,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42243</t>
+          <t>42258</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>66307</t>
+          <t>66486</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>966</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7271</t>
+          <t>8212</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44000</t>
+          <t>43625</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69486</t>
+          <t>70007</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,29%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30595</t>
+          <t>30416</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52262</t>
+          <t>51634</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14033</t>
+          <t>13462</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37731</t>
+          <t>38559</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>62753</t>
+          <t>61805</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>24,98%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10760</t>
+          <t>9518</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26604</t>
+          <t>25474</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10222</t>
+          <t>9827</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14651</t>
+          <t>14326</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32428</t>
+          <t>31689</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>6060</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18080</t>
+          <t>18226</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6684</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20319</t>
+          <t>20778</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>94190</t>
+          <t>93579</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>122147</t>
+          <t>121104</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17488</t>
+          <t>16829</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29413</t>
+          <t>28754</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>115761</t>
+          <t>115868</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>145367</t>
+          <t>145733</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>58,89%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13708</t>
+          <t>13892</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31167</t>
+          <t>30191</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1707</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10772</t>
+          <t>11385</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>16956</t>
+          <t>16640</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>37073</t>
+          <t>36336</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37724</t>
+          <t>37178</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65749</t>
+          <t>64230</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14678</t>
+          <t>13830</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32842</t>
+          <t>31272</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57237</t>
+          <t>56964</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89695</t>
+          <t>87559</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35531</t>
+          <t>35064</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61192</t>
+          <t>62733</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19157</t>
+          <t>18411</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39030</t>
+          <t>37975</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59979</t>
+          <t>59816</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>90670</t>
+          <t>92147</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,32%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26764</t>
+          <t>27852</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52113</t>
+          <t>51465</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6728</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21025</t>
+          <t>21387</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>36874</t>
+          <t>37673</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>65585</t>
+          <t>65621</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7043</t>
+          <t>7263</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22281</t>
+          <t>22007</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>4894</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17409</t>
+          <t>17079</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14912</t>
+          <t>14850</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33960</t>
+          <t>34843</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>174536</t>
+          <t>174098</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>206797</t>
+          <t>208320</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>121881</t>
+          <t>121372</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>148855</t>
+          <t>148727</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>303038</t>
+          <t>303360</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>346791</t>
+          <t>350008</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>69,57%</t>
         </is>
       </c>
     </row>
@@ -7897,12 +7897,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18177</t>
+          <t>17880</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38528</t>
+          <t>37861</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7912,12 +7912,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7932,12 +7932,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17314</t>
+          <t>16915</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>36640</t>
+          <t>37183</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7947,12 +7947,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7967,12 +7967,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>39548</t>
+          <t>38191</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>67430</t>
+          <t>66652</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7982,12 +7982,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5816</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21152</t>
+          <t>21287</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10580</t>
+          <t>11073</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10348</t>
+          <t>9717</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27274</t>
+          <t>26918</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2366</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14782</t>
+          <t>15346</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16951</t>
+          <t>17810</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10743</t>
+          <t>10122</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28419</t>
+          <t>27339</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>8964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24667</t>
+          <t>25805</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>4976</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17371</t>
+          <t>17431</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>16697</t>
+          <t>16690</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>39307</t>
+          <t>36645</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12475</t>
+          <t>13846</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11442</t>
+          <t>11373</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5666</t>
+          <t>5562</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18368</t>
+          <t>19400</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50966</t>
+          <t>50574</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>70977</t>
+          <t>70558</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>64814</t>
+          <t>64472</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>80691</t>
+          <t>81269</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>121674</t>
+          <t>121676</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>148071</t>
+          <t>147158</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>79,68%</t>
         </is>
       </c>
     </row>
@@ -8579,12 +8579,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4907</t>
+          <t>4666</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16715</t>
+          <t>17361</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8594,12 +8594,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8614,12 +8614,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7307</t>
+          <t>7437</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22252</t>
+          <t>21762</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8649,12 +8649,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>13820</t>
+          <t>14162</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>33253</t>
+          <t>33514</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,15%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>97948</t>
+          <t>94682</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>137652</t>
+          <t>134072</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21228</t>
+          <t>20873</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43145</t>
+          <t>42127</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>124792</t>
+          <t>123358</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>168185</t>
+          <t>168823</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>78131</t>
+          <t>78509</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>114668</t>
+          <t>114296</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>34005</t>
+          <t>35152</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>60149</t>
+          <t>59471</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>118433</t>
+          <t>118097</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>163259</t>
+          <t>162470</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,37%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>55773</t>
+          <t>54265</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>90145</t>
+          <t>88587</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>18750</t>
+          <t>18675</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>39519</t>
+          <t>39360</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>81016</t>
+          <t>79798</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>118496</t>
+          <t>117903</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20920</t>
+          <t>20989</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>43763</t>
+          <t>42437</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9269</t>
+          <t>9844</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25349</t>
+          <t>25373</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>34781</t>
+          <t>33807</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>60749</t>
+          <t>61778</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>336690</t>
+          <t>338667</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>384581</t>
+          <t>385053</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>213924</t>
+          <t>214389</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>247900</t>
+          <t>249112</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>564407</t>
+          <t>563252</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>625936</t>
+          <t>622609</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>66,57%</t>
         </is>
       </c>
     </row>
@@ -9261,12 +9261,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>44180</t>
+          <t>43836</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>71387</t>
+          <t>72511</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9296,12 +9296,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>31290</t>
+          <t>32182</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>57955</t>
+          <t>57030</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9331,12 +9331,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>82783</t>
+          <t>82725</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>120963</t>
+          <t>121090</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25A$medico-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P25A$medico-Estudios-trans_orig.xlsx
@@ -943,42 +943,42 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Preocupacion de sus efectos</t>
+          <t>Otros motivos</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17838</t>
+          <t>7526</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11635</t>
+          <t>3219</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27665</t>
+          <t>14660</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>800</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -998,12 +998,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>3370</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1013,42 +1013,42 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>18984</t>
+          <t>8325</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11841</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29251</t>
+          <t>16157</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -1056,52 +1056,52 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Disminucion del rendimiento físico/psíquico</t>
+          <t>Preocupacion de sus efectos</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11295</t>
+          <t>17838</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6262</t>
+          <t>11635</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18749</t>
+          <t>27665</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6331</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1126,42 +1126,42 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>13325</t>
+          <t>18984</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7384</t>
+          <t>11841</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20384</t>
+          <t>29251</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -1169,112 +1169,112 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Propia voluntad</t>
+          <t>Disminucion del rendimiento físico/psíquico</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>146570</t>
+          <t>11295</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>130894</t>
+          <t>6262</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>164376</t>
+          <t>18749</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>36399</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30402</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41379</t>
+          <t>6331</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>182970</t>
+          <t>13325</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>164605</t>
+          <t>7384</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>201412</t>
+          <t>20384</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -1282,112 +1282,112 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Otros motivos</t>
+          <t>Propia voluntad</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>147</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>146570</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>130894</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14660</t>
+          <t>164376</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>36399</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30402</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3370</t>
+          <t>41379</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>182</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>8325</t>
+          <t>182970</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>164605</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>16157</t>
+          <t>201412</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>57,35%</t>
         </is>
       </c>
     </row>
@@ -1625,112 +1625,112 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Preocupacion de sus efectos</t>
+          <t>Otros motivos</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21126</t>
+          <t>4034</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13613</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31202</t>
+          <t>10821</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15753</t>
+          <t>23227</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9178</t>
+          <t>15447</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24971</t>
+          <t>33685</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>36880</t>
+          <t>27262</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>26816</t>
+          <t>19002</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>51297</t>
+          <t>39510</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -1738,112 +1738,112 @@
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Disminucion del rendimiento físico/psíquico</t>
+          <t>Preocupacion de sus efectos</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6808</t>
+          <t>21126</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2844</t>
+          <t>13613</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13249</t>
+          <t>31202</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6645</t>
+          <t>15753</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>9178</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13049</t>
+          <t>24971</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>13454</t>
+          <t>36880</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7669</t>
+          <t>26816</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22154</t>
+          <t>51297</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -1851,112 +1851,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Propia voluntad</t>
+          <t>Disminucion del rendimiento físico/psíquico</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>154063</t>
+          <t>6808</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>139227</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>168061</t>
+          <t>13249</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>96106</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>82712</t>
+          <t>2810</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>108060</t>
+          <t>13049</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>250169</t>
+          <t>13454</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>231233</t>
+          <t>7669</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>267131</t>
+          <t>22154</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -1964,112 +1964,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Otros motivos</t>
+          <t>Propia voluntad</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>148</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4034</t>
+          <t>154063</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>139227</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10821</t>
+          <t>168061</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>94</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23227</t>
+          <t>96106</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15447</t>
+          <t>82712</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33685</t>
+          <t>108060</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>242</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>27262</t>
+          <t>250169</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>19002</t>
+          <t>231233</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>39510</t>
+          <t>267131</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>68,8%</t>
         </is>
       </c>
     </row>
@@ -2307,42 +2307,42 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Preocupacion de sus efectos</t>
+          <t>Otros motivos</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3790</t>
+          <t>826</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15038</t>
+          <t>7132</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2352,67 +2352,67 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>3460</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>968</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9674</t>
+          <t>8263</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>12281</t>
+          <t>6214</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6658</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>21123</t>
+          <t>13954</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -2420,112 +2420,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Disminucion del rendimiento físico/psíquico</t>
+          <t>Preocupacion de sus efectos</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>8612</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3790</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>15038</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9461</t>
+          <t>9674</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>5848</t>
+          <t>12281</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>6658</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11625</t>
+          <t>21123</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>15,55%</t>
         </is>
       </c>
     </row>
@@ -2533,112 +2533,112 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Propia voluntad</t>
+          <t>Disminucion del rendimiento físico/psíquico</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>58316</t>
+          <t>1879</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48719</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66627</t>
+          <t>6498</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>33339</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26247</t>
+          <t>948</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40109</t>
+          <t>9461</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>91655</t>
+          <t>5848</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>80026</t>
+          <t>2081</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>102425</t>
+          <t>11625</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -2646,112 +2646,112 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Otros motivos</t>
+          <t>Propia voluntad</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>58316</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>48719</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>66627</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3460</t>
+          <t>33339</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>26247</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8263</t>
+          <t>40109</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>85</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>6214</t>
+          <t>91655</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2389</t>
+          <t>80026</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>13954</t>
+          <t>102425</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>75,43%</t>
         </is>
       </c>
     </row>
@@ -2989,112 +2989,112 @@
       <c r="A24" s="1" t="n"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Preocupacion de sus efectos</t>
+          <t>Otros motivos</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>47577</t>
+          <t>14314</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36141</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>63195</t>
+          <t>23471</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>20568</t>
+          <t>27487</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13218</t>
+          <t>18728</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>31847</t>
+          <t>38528</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>40</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>68145</t>
+          <t>41800</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>53517</t>
+          <t>30810</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>85331</t>
+          <t>55759</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -3102,112 +3102,112 @@
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Disminucion del rendimiento físico/psíquico</t>
+          <t>Preocupacion de sus efectos</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>48</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>19983</t>
+          <t>47577</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13057</t>
+          <t>36141</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>30053</t>
+          <t>63195</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>12643</t>
+          <t>20568</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7051</t>
+          <t>13218</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20533</t>
+          <t>31847</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>67</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>32626</t>
+          <t>68145</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>22869</t>
+          <t>53517</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>44669</t>
+          <t>85331</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -3215,112 +3215,112 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Propia voluntad</t>
+          <t>Disminucion del rendimiento físico/psíquico</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>358950</t>
+          <t>19983</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>336313</t>
+          <t>13057</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>385026</t>
+          <t>30053</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>165844</t>
+          <t>12643</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>150598</t>
+          <t>7051</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>180176</t>
+          <t>20533</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>34</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>524794</t>
+          <t>32626</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>494299</t>
+          <t>22869</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>553554</t>
+          <t>44669</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -3328,112 +3328,112 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Otros motivos</t>
+          <t>Propia voluntad</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>348</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>14314</t>
+          <t>358950</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>336313</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>23471</t>
+          <t>385026</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>161</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>27487</t>
+          <t>165844</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>18728</t>
+          <t>150598</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>38528</t>
+          <t>180176</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>509</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>41800</t>
+          <t>524794</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>30810</t>
+          <t>494299</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>55759</t>
+          <t>553554</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>63,24%</t>
         </is>
       </c>
     </row>
@@ -3902,42 +3902,42 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Preocupacion de sus efectos</t>
+          <t>Otros motivos</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23097</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13462</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33191</t>
+          <t>15551</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3947,67 +3947,67 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>995</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7812</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>26158</t>
+          <t>10342</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16561</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>37777</t>
+          <t>20818</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -4015,112 +4015,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Disminucion del rendimiento físico/psíquico</t>
+          <t>Preocupacion de sus efectos</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9636</t>
+          <t>23097</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4071</t>
+          <t>13462</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18200</t>
+          <t>33191</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2227</t>
+          <t>3061</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>901</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6688</t>
+          <t>7812</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>24</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>26158</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5726</t>
+          <t>16561</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20614</t>
+          <t>37777</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -4128,112 +4128,112 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Propia voluntad</t>
+          <t>Disminucion del rendimiento físico/psíquico</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>219114</t>
+          <t>9636</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>199902</t>
+          <t>4071</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>235451</t>
+          <t>18200</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>49426</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>41664</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>56699</t>
+          <t>6688</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>268541</t>
+          <t>11864</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>247253</t>
+          <t>5726</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>289650</t>
+          <t>20614</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -4241,112 +4241,112 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Otros motivos</t>
+          <t>Propia voluntad</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>207</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>219114</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2989</t>
+          <t>199902</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15551</t>
+          <t>235451</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>49426</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>41664</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>56699</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>253</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>10342</t>
+          <t>268541</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>247253</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>20818</t>
+          <t>289650</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>65,66%</t>
         </is>
       </c>
     </row>
@@ -4584,112 +4584,112 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Preocupacion de sus efectos</t>
+          <t>Otros motivos</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31154</t>
+          <t>7996</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21789</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>45729</t>
+          <t>14472</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19374</t>
+          <t>14009</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11393</t>
+          <t>7210</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29400</t>
+          <t>22334</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>50528</t>
+          <t>22005</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>36701</t>
+          <t>14593</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>65981</t>
+          <t>32407</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -4697,112 +4697,112 @@
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Disminucion del rendimiento físico/psíquico</t>
+          <t>Preocupacion de sus efectos</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18010</t>
+          <t>31154</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10997</t>
+          <t>21789</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26988</t>
+          <t>45729</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5217</t>
+          <t>19374</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>11393</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13061</t>
+          <t>29400</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>44</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>23228</t>
+          <t>50528</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15074</t>
+          <t>36701</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34674</t>
+          <t>65981</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>11,22%</t>
         </is>
       </c>
     </row>
@@ -4810,112 +4810,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Propia voluntad</t>
+          <t>Disminucion del rendimiento físico/psíquico</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>256366</t>
+          <t>18010</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>240090</t>
+          <t>10997</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>273023</t>
+          <t>26988</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>188593</t>
+          <t>5217</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>173931</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>201372</t>
+          <t>13061</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>444958</t>
+          <t>23228</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>421310</t>
+          <t>15074</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>464930</t>
+          <t>34674</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -4923,112 +4923,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Otros motivos</t>
+          <t>Propia voluntad</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>238</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7996</t>
+          <t>256366</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>240090</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14472</t>
+          <t>273023</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>174</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14009</t>
+          <t>188593</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7210</t>
+          <t>173931</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22334</t>
+          <t>201372</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>412</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>22005</t>
+          <t>444958</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>14593</t>
+          <t>421310</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>32407</t>
+          <t>464930</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>79,09%</t>
         </is>
       </c>
     </row>
@@ -5266,112 +5266,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Preocupacion de sus efectos</t>
+          <t>Otros motivos</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8999</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4368</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15795</t>
+          <t>6564</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4650</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15857</t>
+          <t>7379</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>17926</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11068</t>
+          <t>976</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>27561</t>
+          <t>9360</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -5379,112 +5379,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Disminucion del rendimiento físico/psíquico</t>
+          <t>Preocupacion de sus efectos</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2770</t>
+          <t>8999</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>4368</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7868</t>
+          <t>15795</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4942</t>
+          <t>8927</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>4650</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11051</t>
+          <t>15857</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>17926</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3725</t>
+          <t>11068</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14278</t>
+          <t>27561</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>15,87%</t>
         </is>
       </c>
     </row>
@@ -5492,112 +5492,112 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Propia voluntad</t>
+          <t>Disminucion del rendimiento físico/psíquico</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>74092</t>
+          <t>2770</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>64006</t>
+          <t>886</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>81632</t>
+          <t>7868</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>61637</t>
+          <t>4942</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54142</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>67586</t>
+          <t>11051</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>135730</t>
+          <t>7712</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>122507</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>145215</t>
+          <t>14278</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -5605,112 +5605,112 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Otros motivos</t>
+          <t>Propia voluntad</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>67</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>74092</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>64006</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>81632</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>61637</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>54142</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7379</t>
+          <t>67586</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>120</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>3941</t>
+          <t>135730</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>122507</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9360</t>
+          <t>145215</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>83,62%</t>
         </is>
       </c>
     </row>
@@ -5948,112 +5948,112 @@
       <c r="A24" s="1" t="n"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Preocupacion de sus efectos</t>
+          <t>Otros motivos</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>63249</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>8965</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>80630</t>
+          <t>27330</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>31362</t>
+          <t>19143</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21302</t>
+          <t>11235</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>45371</t>
+          <t>29119</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>34</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>94611</t>
+          <t>36288</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>76889</t>
+          <t>24869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>116045</t>
+          <t>48291</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -6061,112 +6061,112 @@
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Disminucion del rendimiento físico/psíquico</t>
+          <t>Preocupacion de sus efectos</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>58</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>30416</t>
+          <t>63249</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21455</t>
+          <t>48021</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>43465</t>
+          <t>80630</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>12387</t>
+          <t>31362</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7246</t>
+          <t>21302</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23098</t>
+          <t>45371</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>86</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>42803</t>
+          <t>94611</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31715</t>
+          <t>76889</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>59310</t>
+          <t>116045</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -6174,112 +6174,112 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Propia voluntad</t>
+          <t>Disminucion del rendimiento físico/psíquico</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>549572</t>
+          <t>30416</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>521546</t>
+          <t>21455</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>576324</t>
+          <t>43465</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>299655</t>
+          <t>12387</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>283419</t>
+          <t>7246</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>315071</t>
+          <t>23098</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>40</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>849228</t>
+          <t>42803</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>817611</t>
+          <t>31715</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>883544</t>
+          <t>59310</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -6287,112 +6287,112 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Otros motivos</t>
+          <t>Propia voluntad</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>512</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>17144</t>
+          <t>549572</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8965</t>
+          <t>521546</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>27330</t>
+          <t>576324</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>273</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>19143</t>
+          <t>299655</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>11235</t>
+          <t>283419</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>29119</t>
+          <t>315071</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>785</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>36288</t>
+          <t>849228</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>24869</t>
+          <t>817611</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>48291</t>
+          <t>883544</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>73,47%</t>
         </is>
       </c>
     </row>
@@ -6861,112 +6861,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Preocupacion de sus efectos</t>
+          <t>Otros motivos</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16918</t>
+          <t>20959</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9518</t>
+          <t>13892</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25474</t>
+          <t>30191</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4952</t>
+          <t>4927</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9827</t>
+          <t>11385</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>21870</t>
+          <t>25886</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14326</t>
+          <t>16640</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31689</t>
+          <t>36336</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -6974,112 +6974,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Disminucion del rendimiento físico/psíquico</t>
+          <t>Preocupacion de sus efectos</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11176</t>
+          <t>16918</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6060</t>
+          <t>9518</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18226</t>
+          <t>25474</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>9827</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>12212</t>
+          <t>21870</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6859</t>
+          <t>14326</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20778</t>
+          <t>31689</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -7087,112 +7087,112 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Propia voluntad</t>
+          <t>Disminucion del rendimiento físico/psíquico</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>107572</t>
+          <t>11176</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>93579</t>
+          <t>6060</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>121104</t>
+          <t>18226</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>23332</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16829</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28754</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>130904</t>
+          <t>12212</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>115868</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>145733</t>
+          <t>20778</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -7200,112 +7200,112 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Otros motivos</t>
+          <t>Propia voluntad</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>113</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20959</t>
+          <t>107572</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13892</t>
+          <t>93579</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30191</t>
+          <t>121104</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4927</t>
+          <t>23332</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>16829</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11385</t>
+          <t>28754</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>135</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>25886</t>
+          <t>130904</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>16640</t>
+          <t>115868</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>36336</t>
+          <t>145733</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>58,89%</t>
         </is>
       </c>
     </row>
@@ -7543,112 +7543,112 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Preocupacion de sus efectos</t>
+          <t>Otros motivos</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>37982</t>
+          <t>26908</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27852</t>
+          <t>17880</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51465</t>
+          <t>37861</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12488</t>
+          <t>25219</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>16915</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21387</t>
+          <t>37183</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>49</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>50470</t>
+          <t>52127</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>37673</t>
+          <t>38191</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>65621</t>
+          <t>66652</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -7656,112 +7656,112 @@
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Disminucion del rendimiento físico/psíquico</t>
+          <t>Preocupacion de sus efectos</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>37982</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>27852</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>51465</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,57%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9,22%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>17,04%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>13558</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7263</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>22007</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4,49%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,29%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9871</t>
+          <t>12488</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4894</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17079</t>
+          <t>21387</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>47</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>23430</t>
+          <t>50470</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14850</t>
+          <t>37673</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34843</t>
+          <t>65621</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -7769,112 +7769,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Propia voluntad</t>
+          <t>Disminucion del rendimiento físico/psíquico</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>191349</t>
+          <t>13558</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>174098</t>
+          <t>7263</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>208320</t>
+          <t>22007</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>135473</t>
+          <t>9871</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>121372</t>
+          <t>4894</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>148727</t>
+          <t>17079</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>326823</t>
+          <t>23430</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>303360</t>
+          <t>14850</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>350008</t>
+          <t>34843</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -7882,112 +7882,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Otros motivos</t>
+          <t>Propia voluntad</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>181</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26908</t>
+          <t>191349</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17880</t>
+          <t>174098</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>37861</t>
+          <t>208320</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>127</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25219</t>
+          <t>135473</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16915</t>
+          <t>121372</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>37183</t>
+          <t>148727</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>308</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>52127</t>
+          <t>326823</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>38191</t>
+          <t>303360</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>66652</t>
+          <t>350008</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>69,57%</t>
         </is>
       </c>
     </row>
@@ -8225,112 +8225,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Preocupacion de sus efectos</t>
+          <t>Otros motivos</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15681</t>
+          <t>9459</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8964</t>
+          <t>4666</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25805</t>
+          <t>17361</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10022</t>
+          <t>13115</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>7437</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17431</t>
+          <t>21762</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>25702</t>
+          <t>22573</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>16690</t>
+          <t>14162</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>36645</t>
+          <t>33514</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>18,15%</t>
         </is>
       </c>
     </row>
@@ -8338,112 +8338,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Disminucion del rendimiento físico/psíquico</t>
+          <t>Preocupacion de sus efectos</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>15681</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>8964</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13846</t>
+          <t>25805</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>10022</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>4976</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11373</t>
+          <t>17431</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>10850</t>
+          <t>25702</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5562</t>
+          <t>16690</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19400</t>
+          <t>36645</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -8451,112 +8451,112 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Propia voluntad</t>
+          <t>Disminucion del rendimiento físico/psíquico</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>62244</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50574</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>70558</t>
+          <t>13846</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>73437</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>64472</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>81269</t>
+          <t>11373</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>135681</t>
+          <t>10850</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>121676</t>
+          <t>5562</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>147158</t>
+          <t>19400</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -8564,112 +8564,112 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Otros motivos</t>
+          <t>Propia voluntad</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>56</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9459</t>
+          <t>62244</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>50574</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17361</t>
+          <t>70558</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>67</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13115</t>
+          <t>73437</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7437</t>
+          <t>64472</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21762</t>
+          <t>81269</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>123</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>22573</t>
+          <t>135681</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14162</t>
+          <t>121676</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>33514</t>
+          <t>147158</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>79,68%</t>
         </is>
       </c>
     </row>
@@ -8907,112 +8907,112 @@
       <c r="A24" s="1" t="n"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Preocupacion de sus efectos</t>
+          <t>Otros motivos</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>70580</t>
+          <t>57326</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>54265</t>
+          <t>43836</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>88587</t>
+          <t>72511</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>27462</t>
+          <t>43260</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>18675</t>
+          <t>32182</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>39360</t>
+          <t>57030</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>95</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>98042</t>
+          <t>100586</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>79798</t>
+          <t>82725</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>117903</t>
+          <t>121090</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -9020,112 +9020,112 @@
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Disminucion del rendimiento físico/psíquico</t>
+          <t>Preocupacion de sus efectos</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>30384</t>
+          <t>70580</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20989</t>
+          <t>54265</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42437</t>
+          <t>88587</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>16107</t>
+          <t>27462</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9844</t>
+          <t>18675</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25373</t>
+          <t>39360</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>92</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>46491</t>
+          <t>98042</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33807</t>
+          <t>79798</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>61778</t>
+          <t>117903</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -9133,112 +9133,112 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Propia voluntad</t>
+          <t>Disminucion del rendimiento físico/psíquico</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>361165</t>
+          <t>30384</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>338667</t>
+          <t>20989</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>385053</t>
+          <t>42437</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>232242</t>
+          <t>16107</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>214389</t>
+          <t>9844</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>249112</t>
+          <t>25373</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>593407</t>
+          <t>46491</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>563252</t>
+          <t>33807</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>622609</t>
+          <t>61778</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -9246,112 +9246,112 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Otros motivos</t>
+          <t>Propia voluntad</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>350</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>57326</t>
+          <t>361165</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>43836</t>
+          <t>338667</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>72511</t>
+          <t>385053</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>216</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>43260</t>
+          <t>232242</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>32182</t>
+          <t>214389</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>57030</t>
+          <t>249112</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>566</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>100586</t>
+          <t>593407</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>82725</t>
+          <t>563252</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>121090</t>
+          <t>622609</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>66,57%</t>
         </is>
       </c>
     </row>
